--- a/inputs/data_symbols_TD/13_LTAN06_800km_1213COLD_MY_STTLCT_PROP_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/13_LTAN06_800km_1213COLD_MY_STTLCT_PROP_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07FEE9E8-895D-4E6F-B5AA-01A57C1BA635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3539388B-642B-4AB0-AB1C-E3DC5D69E3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{CFC0C9FC-7A14-41E0-8556-51C4CBBF91E1}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{44274546-30DA-4C2D-85AB-2DD1AA50B7A5}"/>
   </bookViews>
   <sheets>
     <sheet name="13_LTAN06_800km_1213COLD_MY_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{390FA034-D30D-4337-8269-7A997AC3B914}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20F5757E-8A82-4D5A-B88A-B5D1D3C04CF3}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>97.984549999999999</v>
+        <v>88.964039999999997</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>97.984549999999999</v>
+        <v>88.964039999999997</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>97.984849999999994</v>
+        <v>88.96405</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>97.985960000000006</v>
+        <v>88.964190000000002</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>97.98818</v>
+        <v>88.964699999999993</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>97.991720000000001</v>
+        <v>88.965710000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>97.996759999999995</v>
+        <v>88.967349999999996</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>98.003479999999996</v>
+        <v>88.969729999999998</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>98.011989999999997</v>
+        <v>88.972949999999997</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>98.022450000000006</v>
+        <v>88.977099999999993</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>98.034949999999995</v>
+        <v>88.982249999999993</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>98.049589999999995</v>
+        <v>88.988470000000007</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>98.066429999999997</v>
+        <v>88.995819999999995</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>98.085539999999995</v>
+        <v>89.004329999999996</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>98.106909999999999</v>
+        <v>89.014020000000002</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>98.130570000000006</v>
+        <v>89.024929999999998</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>98.156480000000002</v>
+        <v>89.037049999999994</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>98.184619999999995</v>
+        <v>89.050389999999993</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>98.214939999999999</v>
+        <v>89.064930000000004</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>98.243549999999999</v>
+        <v>89.078819999999993</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1311,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>98.265979999999999</v>
+        <v>89.0899</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>98.281289999999998</v>
+        <v>89.097660000000005</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="D24">
-        <v>98.28877</v>
+        <v>89.101690000000005</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1353,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>98.287760000000006</v>
+        <v>89.101579999999998</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>98.277609999999996</v>
+        <v>89.096940000000004</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -1381,7 +1381,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>98.257720000000006</v>
+        <v>89.087389999999999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>98.227530000000002</v>
+        <v>89.072550000000007</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>98.186589999999995</v>
+        <v>89.052130000000005</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="D30">
-        <v>98.134540000000001</v>
+        <v>89.025859999999994</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -1437,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>98.071169999999995</v>
+        <v>88.993539999999996</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
@@ -1451,7 +1451,7 @@
         <v>3</v>
       </c>
       <c r="D32">
-        <v>97.996340000000004</v>
+        <v>88.95505</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>97.910070000000005</v>
+        <v>88.910300000000007</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -1479,7 +1479,7 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>97.812449999999998</v>
+        <v>88.859290000000001</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>97.703680000000006</v>
+        <v>88.802059999999997</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>97.584040000000002</v>
+        <v>88.738699999999994</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
@@ -1521,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>97.45384</v>
+        <v>88.669340000000005</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>97.316609999999997</v>
+        <v>88.595759999999999</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>97.176429999999996</v>
+        <v>88.520060000000001</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>97.034670000000006</v>
+        <v>88.442899999999995</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>96.892579999999995</v>
+        <v>88.364930000000001</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>96.751369999999994</v>
+        <v>88.286749999999998</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>96.612229999999997</v>
+        <v>88.209000000000003</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>96.476330000000004</v>
+        <v>88.132289999999998</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>96.344729999999998</v>
+        <v>88.057199999999995</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>96.218400000000003</v>
+        <v>87.984279999999998</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>96.098190000000002</v>
+        <v>87.914000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>95.984780000000001</v>
+        <v>87.846770000000006</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>95.878699999999995</v>
+        <v>87.782929999999993</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>95.780360000000002</v>
+        <v>87.722750000000005</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>95.690010000000001</v>
+        <v>87.666420000000002</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>95.607810000000001</v>
+        <v>87.614080000000001</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>95.533799999999999</v>
+        <v>87.565809999999999</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>95.467929999999996</v>
+        <v>87.521680000000003</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>95.410120000000006</v>
+        <v>87.481669999999994</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>95.36018</v>
+        <v>87.445779999999999</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>95.317939999999993</v>
+        <v>87.413970000000006</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>95.283159999999995</v>
+        <v>87.386189999999999</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>95.255579999999995</v>
+        <v>87.362359999999995</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>95.234920000000002</v>
+        <v>87.342410000000001</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>95.220889999999997</v>
+        <v>87.326250000000002</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>95.213170000000005</v>
+        <v>87.313749999999999</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>95.211470000000006</v>
+        <v>87.304820000000007</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>95.215450000000004</v>
+        <v>87.299319999999994</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>95.224779999999996</v>
+        <v>87.297110000000004</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>95.239159999999998</v>
+        <v>87.29804</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>95.258260000000007</v>
+        <v>87.30198</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>95.281760000000006</v>
+        <v>87.308769999999996</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>95.309349999999995</v>
+        <v>87.318240000000003</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>95.340710000000001</v>
+        <v>87.33023</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>95.375550000000004</v>
+        <v>87.344610000000003</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>95.413600000000002</v>
+        <v>87.361199999999997</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>95.454589999999996</v>
+        <v>87.379890000000003</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>95.498260000000002</v>
+        <v>87.400490000000005</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>95.544340000000005</v>
+        <v>87.422830000000005</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>95.592600000000004</v>
+        <v>87.446770000000001</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>95.642790000000005</v>
+        <v>87.472160000000002</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>95.694670000000002</v>
+        <v>87.498840000000001</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>95.748050000000006</v>
+        <v>87.526690000000002</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>95.802729999999997</v>
+        <v>87.55556</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>95.858540000000005</v>
+        <v>87.585329999999999</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>95.915319999999994</v>
+        <v>87.615870000000001</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>95.972890000000007</v>
+        <v>87.647080000000003</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>96.031120000000001</v>
+        <v>87.678839999999994</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>96.089870000000005</v>
+        <v>87.711060000000003</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>96.149029999999996</v>
+        <v>87.743650000000002</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>96.208479999999994</v>
+        <v>87.776529999999994</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>96.268129999999999</v>
+        <v>87.809640000000002</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>96.327889999999996</v>
+        <v>87.842889999999997</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>96.387690000000006</v>
+        <v>87.876239999999996</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>96.447479999999999</v>
+        <v>87.909630000000007</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>96.507220000000004</v>
+        <v>87.943020000000004</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>96.566850000000002</v>
+        <v>87.976370000000003</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>96.626339999999999</v>
+        <v>88.009649999999993</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>96.685680000000005</v>
+        <v>88.042839999999998</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>96.744829999999993</v>
+        <v>88.075919999999996</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>96.803799999999995</v>
+        <v>88.108869999999996</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>96.862579999999994</v>
+        <v>88.1417</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>96.921170000000004</v>
+        <v>88.174400000000006</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>96.979579999999999</v>
+        <v>88.206959999999995</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>97.037819999999996</v>
+        <v>88.239419999999996</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>97.095920000000007</v>
+        <v>88.271780000000007</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>97.153899999999993</v>
+        <v>88.304079999999999</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>97.211799999999997</v>
+        <v>88.336330000000004</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>97.269630000000006</v>
+        <v>88.368560000000002</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>97.327439999999996</v>
+        <v>88.400790000000001</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>97.385230000000007</v>
+        <v>88.433030000000002</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>97.443049999999999</v>
+        <v>88.465320000000006</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>97.500910000000005</v>
+        <v>88.497659999999996</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>97.558819999999997</v>
+        <v>88.530079999999998</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>97.616810000000001</v>
+        <v>88.56259</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>97.674899999999994</v>
+        <v>88.595209999999994</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>97.733109999999996</v>
+        <v>88.627949999999998</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>97.791470000000004</v>
+        <v>88.660820000000001</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>97.85</v>
+        <v>88.693839999999994</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>97.908709999999999</v>
+        <v>88.727010000000007</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>97.967619999999997</v>
+        <v>88.760339999999999</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>98.026740000000004</v>
+        <v>88.793850000000006</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>98.086079999999995</v>
+        <v>88.827529999999996</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>98.145650000000003</v>
+        <v>88.861400000000003</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
@@ -2697,7 +2697,7 @@
         <v>3</v>
       </c>
       <c r="D121">
-        <v>98.201589999999996</v>
+        <v>88.893609999999995</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
@@ -2711,7 +2711,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>98.249449999999996</v>
+        <v>88.921999999999997</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="D123">
-        <v>98.288380000000004</v>
+        <v>88.946110000000004</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="D124">
-        <v>98.317750000000004</v>
+        <v>88.965549999999993</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
@@ -2753,7 +2753,7 @@
         <v>3</v>
       </c>
       <c r="D125">
-        <v>98.33699</v>
+        <v>88.979950000000002</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="D126">
-        <v>98.345550000000003</v>
+        <v>88.988950000000003</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
@@ -2781,7 +2781,7 @@
         <v>3</v>
       </c>
       <c r="D127">
-        <v>98.342910000000003</v>
+        <v>88.99221</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
@@ -2795,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="D128">
-        <v>98.328609999999998</v>
+        <v>88.989419999999996</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
@@ -2809,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>98.302269999999993</v>
+        <v>88.980279999999993</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
@@ -2823,7 +2823,7 @@
         <v>3</v>
       </c>
       <c r="D130">
-        <v>98.263620000000003</v>
+        <v>88.964590000000001</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
@@ -2837,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="D131">
-        <v>98.212540000000004</v>
+        <v>88.942179999999993</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
@@ -2851,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="D132">
-        <v>98.148979999999995</v>
+        <v>88.912959999999998</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
@@ -2865,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>98.072999999999993</v>
+        <v>88.876890000000003</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
@@ -2879,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="D134">
-        <v>97.984780000000001</v>
+        <v>88.834000000000003</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
@@ -2893,7 +2893,7 @@
         <v>3</v>
       </c>
       <c r="D135">
-        <v>97.88458</v>
+        <v>88.784360000000007</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="D136">
-        <v>97.772739999999999</v>
+        <v>88.728089999999995</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
@@ -2921,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="D137">
-        <v>97.649640000000005</v>
+        <v>88.665329999999997</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>97.518870000000007</v>
+        <v>88.597939999999994</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>97.384569999999997</v>
+        <v>88.528019999999998</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>97.248170000000002</v>
+        <v>88.45626</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>97.110950000000003</v>
+        <v>88.383340000000004</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>96.974170000000001</v>
+        <v>88.309880000000007</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>96.839060000000003</v>
+        <v>88.236540000000005</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>96.706800000000001</v>
+        <v>88.16395</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>96.578490000000002</v>
+        <v>88.092709999999997</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>96.45514</v>
+        <v>88.023380000000003</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>96.337590000000006</v>
+        <v>87.956450000000004</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>96.226569999999995</v>
+        <v>87.892359999999996</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>96.122619999999998</v>
+        <v>87.831429999999997</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>96.026160000000004</v>
+        <v>87.773970000000006</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>95.937479999999994</v>
+        <v>87.720169999999996</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>95.856729999999999</v>
+        <v>87.670180000000002</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>95.78398</v>
+        <v>87.624110000000002</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>95.719189999999998</v>
+        <v>87.582009999999997</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>95.662279999999996</v>
+        <v>87.543899999999994</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>95.613100000000003</v>
+        <v>87.50976</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>95.571460000000002</v>
+        <v>87.479569999999995</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>95.537139999999994</v>
+        <v>87.453289999999996</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>95.509889999999999</v>
+        <v>87.430859999999996</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>95.489450000000005</v>
+        <v>87.412189999999995</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>95.475520000000003</v>
+        <v>87.397210000000001</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>95.46781</v>
+        <v>87.385810000000006</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>95.466009999999997</v>
+        <v>87.377870000000001</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>95.469800000000006</v>
+        <v>87.373289999999997</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>95.478870000000001</v>
+        <v>87.371920000000003</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>95.492900000000006</v>
+        <v>87.373620000000003</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>95.511579999999995</v>
+        <v>87.378259999999997</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>95.534599999999998</v>
+        <v>87.385679999999994</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="D169">
-        <v>95.561639999999997</v>
+        <v>87.395719999999997</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>95.592389999999995</v>
+        <v>87.408230000000003</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>95.626580000000004</v>
+        <v>87.423069999999996</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>95.663929999999993</v>
+        <v>87.440079999999995</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>95.704170000000005</v>
+        <v>87.459130000000002</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>95.747050000000002</v>
+        <v>87.480050000000006</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="D175">
-        <v>95.792310000000001</v>
+        <v>87.502679999999998</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>95.839699999999993</v>
+        <v>87.526859999999999</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>95.888990000000007</v>
+        <v>87.552449999999993</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>95.939959999999999</v>
+        <v>87.579310000000007</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>95.99239</v>
+        <v>87.607299999999995</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>96.046099999999996</v>
+        <v>87.636279999999999</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>96.100920000000002</v>
+        <v>87.666129999999995</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>96.156679999999994</v>
+        <v>87.696730000000002</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>96.213229999999996</v>
+        <v>87.727969999999999</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>96.270409999999998</v>
+        <v>87.759749999999997</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>96.328109999999995</v>
+        <v>87.791960000000003</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>96.386189999999999</v>
+        <v>87.824520000000007</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>96.444559999999996</v>
+        <v>87.85736</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>96.503119999999996</v>
+        <v>87.890389999999996</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>96.561779999999999</v>
+        <v>87.923569999999998</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>96.620480000000001</v>
+        <v>87.956829999999997</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>96.679159999999996</v>
+        <v>87.990110000000001</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>96.737769999999998</v>
+        <v>88.023380000000003</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>96.796279999999996</v>
+        <v>88.05659</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>96.854659999999996</v>
+        <v>88.089730000000003</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>96.912859999999995</v>
+        <v>88.12276</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="D196">
-        <v>96.970889999999997</v>
+        <v>88.155680000000004</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>97.028729999999996</v>
+        <v>88.188460000000006</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>97.086380000000005</v>
+        <v>88.221109999999996</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>97.143839999999997</v>
+        <v>88.253619999999998</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>97.201120000000003</v>
+        <v>88.285989999999998</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>97.258229999999998</v>
+        <v>88.318240000000003</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>97.315200000000004</v>
+        <v>88.350399999999993</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="D203">
-        <v>97.372060000000005</v>
+        <v>88.382480000000001</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>97.428830000000005</v>
+        <v>88.414519999999996</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>97.485550000000003</v>
+        <v>88.446520000000007</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>97.542230000000004</v>
+        <v>88.478520000000003</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>97.598920000000007</v>
+        <v>88.510540000000006</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>97.655619999999999</v>
+        <v>88.542590000000004</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>97.712370000000007</v>
+        <v>88.574690000000004</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>97.769180000000006</v>
+        <v>88.606870000000001</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="D211">
-        <v>97.826070000000001</v>
+        <v>88.639129999999994</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>97.88306</v>
+        <v>88.671499999999995</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.4">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="D213">
-        <v>97.940179999999998</v>
+        <v>88.703999999999994</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="D214">
-        <v>97.997460000000004</v>
+        <v>88.736620000000002</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="D215">
-        <v>98.054900000000004</v>
+        <v>88.769379999999998</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="D216">
-        <v>98.112539999999996</v>
+        <v>88.802300000000002</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>98.170370000000005</v>
+        <v>88.835380000000001</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="D218">
-        <v>98.22842</v>
+        <v>88.868629999999996</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D219">
-        <v>98.286699999999996</v>
+        <v>88.902050000000003</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="D220">
-        <v>98.345209999999994</v>
+        <v>88.935659999999999</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
@@ -4097,7 +4097,7 @@
         <v>3</v>
       </c>
       <c r="D221">
-        <v>98.400090000000006</v>
+        <v>88.967609999999993</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>3</v>
       </c>
       <c r="D222">
-        <v>98.446889999999996</v>
+        <v>88.995739999999998</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.4">
@@ -4125,7 +4125,7 @@
         <v>3</v>
       </c>
       <c r="D223">
-        <v>98.484750000000005</v>
+        <v>89.019580000000005</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.4">
@@ -4139,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="D224">
-        <v>98.513050000000007</v>
+        <v>89.038749999999993</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.4">
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="D225">
-        <v>98.531220000000005</v>
+        <v>89.052869999999999</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.4">
@@ -4167,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>98.538700000000006</v>
+        <v>89.061599999999999</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.4">
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="D227">
-        <v>98.534980000000004</v>
+        <v>89.064589999999995</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.4">
@@ -4195,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="D228">
-        <v>98.519599999999997</v>
+        <v>89.061509999999998</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.4">
@@ -4209,7 +4209,7 @@
         <v>3</v>
       </c>
       <c r="D229">
-        <v>98.492180000000005</v>
+        <v>89.052099999999996</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.4">
@@ -4223,7 +4223,7 @@
         <v>3</v>
       </c>
       <c r="D230">
-        <v>98.452449999999999</v>
+        <v>89.036119999999997</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.4">
@@ -4237,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>98.400289999999998</v>
+        <v>89.01343</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.4">
@@ -4251,7 +4251,7 @@
         <v>3</v>
       </c>
       <c r="D232">
-        <v>98.335650000000001</v>
+        <v>88.983919999999998</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.4">
@@ -4265,7 +4265,7 @@
         <v>3</v>
       </c>
       <c r="D233">
-        <v>98.258589999999998</v>
+        <v>88.947569999999999</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.4">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D234">
-        <v>98.169300000000007</v>
+        <v>88.904390000000006</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.4">
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="D235">
-        <v>98.068039999999996</v>
+        <v>88.854460000000003</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.4">
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>97.95514</v>
+        <v>88.797899999999998</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.4">
@@ -4321,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="D237">
-        <v>97.831000000000003</v>
+        <v>88.734859999999998</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.4">
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>97.699179999999998</v>
+        <v>88.667190000000005</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.4">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="D239">
-        <v>97.563860000000005</v>
+        <v>88.596969999999999</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="D240">
-        <v>97.426450000000003</v>
+        <v>88.524940000000001</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.4">
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="D241">
-        <v>97.288240000000002</v>
+        <v>88.451740000000001</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.4">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="D242">
-        <v>97.150490000000005</v>
+        <v>88.378010000000003</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.4">
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="D243">
-        <v>97.014420000000001</v>
+        <v>88.304400000000001</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="D244">
-        <v>96.881219999999999</v>
+        <v>88.231539999999995</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.4">
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="D245">
-        <v>96.751990000000006</v>
+        <v>88.160039999999995</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.4">
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="D246">
-        <v>96.62773</v>
+        <v>88.090450000000004</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.4">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>96.509299999999996</v>
+        <v>88.023269999999997</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D248">
-        <v>96.397390000000001</v>
+        <v>87.958910000000003</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.4">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>96.292580000000001</v>
+        <v>87.897739999999999</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.4">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="D250">
-        <v>96.195279999999997</v>
+        <v>87.840019999999996</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.4">
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>96.105760000000004</v>
+        <v>87.785979999999995</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.4">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="D252">
-        <v>96.024180000000001</v>
+        <v>87.735749999999996</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.4">
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="D253">
-        <v>95.950609999999998</v>
+        <v>87.689440000000005</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.4">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>95.885009999999994</v>
+        <v>87.647099999999995</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.4">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>95.827299999999994</v>
+        <v>87.608750000000001</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.4">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>95.777320000000003</v>
+        <v>87.574380000000005</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.4">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>95.734889999999993</v>
+        <v>87.543949999999995</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.4">
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>95.699789999999993</v>
+        <v>87.517439999999993</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.4">
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>95.671760000000006</v>
+        <v>87.494780000000006</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.4">
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>95.650549999999996</v>
+        <v>87.475880000000004</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.4">
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>95.635850000000005</v>
+        <v>87.460669999999993</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.4">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="D262">
-        <v>95.627369999999999</v>
+        <v>87.449039999999997</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.4">
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="D263">
-        <v>95.624799999999993</v>
+        <v>87.440880000000007</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.4">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="D264">
-        <v>95.627840000000006</v>
+        <v>87.436070000000001</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.4">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="D265">
-        <v>95.636150000000001</v>
+        <v>87.434470000000005</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.4">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="D266">
-        <v>95.649420000000006</v>
+        <v>87.435950000000005</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.4">
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="D267">
-        <v>95.667349999999999</v>
+        <v>87.440359999999998</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.4">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="D268">
-        <v>95.689620000000005</v>
+        <v>87.447559999999996</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.4">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="D269">
-        <v>95.715909999999994</v>
+        <v>87.457380000000001</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.4">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="D270">
-        <v>95.745909999999995</v>
+        <v>87.469669999999994</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.4">
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>95.779359999999997</v>
+        <v>87.484279999999998</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.4">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="D272">
-        <v>95.815960000000004</v>
+        <v>87.501069999999999</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="D273">
-        <v>95.855459999999994</v>
+        <v>87.519900000000007</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.4">
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="D274">
-        <v>95.897599999999997</v>
+        <v>87.540599999999998</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.4">
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="D275">
-        <v>95.94211</v>
+        <v>87.563010000000006</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.4">
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="D276">
-        <v>95.988770000000002</v>
+        <v>87.586969999999994</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="D277">
-        <v>96.037329999999997</v>
+        <v>87.612340000000003</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.4">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="D278">
-        <v>96.087559999999996</v>
+        <v>87.638980000000004</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.4">
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D279">
-        <v>96.139250000000004</v>
+        <v>87.666749999999993</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.4">
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="D280">
-        <v>96.192239999999998</v>
+        <v>87.695520000000002</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="D281">
-        <v>96.24633</v>
+        <v>87.725149999999999</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.4">
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="D282">
-        <v>96.301360000000003</v>
+        <v>87.755529999999993</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.4">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="D283">
-        <v>96.35718</v>
+        <v>87.786550000000005</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.4">
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>96.413640000000001</v>
+        <v>87.818110000000004</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="D285">
-        <v>96.470609999999994</v>
+        <v>87.850110000000001</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.4">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D286">
-        <v>96.527979999999999</v>
+        <v>87.882450000000006</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.4">
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="D287">
-        <v>96.585629999999995</v>
+        <v>87.91507</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.4">
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="D288">
-        <v>96.643469999999994</v>
+        <v>87.947890000000001</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.4">
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="D289">
-        <v>96.701419999999999</v>
+        <v>87.980860000000007</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.4">
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>96.759399999999999</v>
+        <v>88.013900000000007</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.4">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="D291">
-        <v>96.81738</v>
+        <v>88.046959999999999</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.4">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>96.875290000000007</v>
+        <v>88.080020000000005</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.4">
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="D293">
-        <v>96.933090000000007</v>
+        <v>88.113020000000006</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.4">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="D294">
-        <v>96.990759999999995</v>
+        <v>88.145939999999996</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.4">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="D295">
-        <v>97.048270000000002</v>
+        <v>88.178759999999997</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.4">
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D296">
-        <v>97.105599999999995</v>
+        <v>88.211460000000002</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.4">
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="D297">
-        <v>97.162739999999999</v>
+        <v>88.244039999999998</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.4">
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>97.219700000000003</v>
+        <v>88.276470000000003</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.4">
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>97.276470000000003</v>
+        <v>88.308769999999996</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="D300">
-        <v>97.333070000000006</v>
+        <v>88.34093</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.4">
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="D301">
-        <v>97.389489999999995</v>
+        <v>88.372979999999998</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.4">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="D302">
-        <v>97.445779999999999</v>
+        <v>88.404920000000004</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.4">
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="D303">
-        <v>97.501959999999997</v>
+        <v>88.436800000000005</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_symbols_TD/13_LTAN06_800km_1213COLD_MY_STTLCT_PROP_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/13_LTAN06_800km_1213COLD_MY_STTLCT_PROP_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3539388B-642B-4AB0-AB1C-E3DC5D69E3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{530C40A7-CE93-46DC-BB1D-366907C161DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{44274546-30DA-4C2D-85AB-2DD1AA50B7A5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DD3985D2-02A1-43F9-B25A-948040A5B43B}"/>
   </bookViews>
   <sheets>
     <sheet name="13_LTAN06_800km_1213COLD_MY_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20F5757E-8A82-4D5A-B88A-B5D1D3C04CF3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74FB9226-E47B-4857-9F4F-695A3373DFD3}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/13_LTAN06_800km_1213COLD_MY_STTLCT_PROP_HEAT_MY_0p5.xlsx
+++ b/inputs/data_symbols_TD/13_LTAN06_800km_1213COLD_MY_STTLCT_PROP_HEAT_MY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{530C40A7-CE93-46DC-BB1D-366907C161DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCFA89F2-94BC-4050-B0CE-D8CE27120E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DD3985D2-02A1-43F9-B25A-948040A5B43B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{8DF31D02-180A-4FE3-B13D-99B40F206CAF}"/>
   </bookViews>
   <sheets>
     <sheet name="13_LTAN06_800km_1213COLD_MY_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74FB9226-E47B-4857-9F4F-695A3373DFD3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A1871B-577B-4249-B184-4A3B62BA8C0A}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
